--- a/data/trans_orig/P1430-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1430-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cirrosis en 2012</t>
+          <t>Población con diagnóstico de cirrosis en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28653</t>
+          <t>27674</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24473</t>
+          <t>23332</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21095</t>
+          <t>20126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45752</t>
+          <t>44438</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>945990</t>
+          <t>946969</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>965149</t>
+          <t>965768</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1313324</t>
+          <t>1314465</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1330346</t>
+          <t>1330284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2266688</t>
+          <t>2268002</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2291345</t>
+          <t>2292314</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14881</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15804</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10008</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25844</t>
+          <t>27743</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1949076</t>
+          <t>1948282</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1960084</t>
+          <t>1959906</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1738788</t>
+          <t>1739068</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1750482</t>
+          <t>1750523</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3692705</t>
+          <t>3690806</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3708541</t>
+          <t>3708864</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -1417,97 +1417,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2104</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2121</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>481181</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>456499</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>458631</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>937692</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>939813</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15704</t>
+          <t>15309</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37033</t>
+          <t>37224</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13971</t>
+          <t>13871</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33903</t>
+          <t>33071</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34840</t>
+          <t>33791</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63315</t>
+          <t>63083</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3382749</t>
+          <t>3382558</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3404078</t>
+          <t>3404473</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3517117</t>
+          <t>3517949</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3537049</t>
+          <t>3537149</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6907486</t>
+          <t>6907718</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6935961</t>
+          <t>6937010</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cirrosis en 2016</t>
+          <t>Población con diagnóstico de cirrosis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15722</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20846</t>
+          <t>20621</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>742708</t>
+          <t>743150</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>752540</t>
+          <t>752536</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>978938</t>
+          <t>980486</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>992561</t>
+          <t>992639</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1728161</t>
+          <t>1728386</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1743435</t>
+          <t>1743713</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24696</t>
+          <t>22608</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>12563</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11367</t>
+          <t>11511</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30242</t>
+          <t>30247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2051689</t>
+          <t>2053777</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2069148</t>
+          <t>2069446</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1975150</t>
+          <t>1975737</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1986298</t>
+          <t>1986311</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4034443</t>
+          <t>4034438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4053318</t>
+          <t>4053174</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15147</t>
+          <t>15449</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17492</t>
+          <t>16758</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531739</t>
+          <t>531437</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>544856</t>
+          <t>544811</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>542733</t>
+          <t>542784</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1078535</t>
+          <t>1079269</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1092430</t>
+          <t>1092396</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15909</t>
+          <t>15427</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37482</t>
+          <t>37608</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>7691</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23997</t>
+          <t>23729</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27036</t>
+          <t>27019</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54150</t>
+          <t>53373</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3340136</t>
+          <t>3340010</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3361709</t>
+          <t>3362191</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3508103</t>
+          <t>3508371</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3525278</t>
+          <t>3524409</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6855568</t>
+          <t>6856345</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6882682</t>
+          <t>6882699</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/P1430-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1430-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8875</t>
+          <t>9272</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27674</t>
+          <t>27436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>7679</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23332</t>
+          <t>23568</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>20747</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44438</t>
+          <t>45035</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>946969</t>
+          <t>947207</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>965768</t>
+          <t>965371</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1314465</t>
+          <t>1314229</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1330284</t>
+          <t>1330118</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2268002</t>
+          <t>2267405</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2292314</t>
+          <t>2291693</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15675</t>
+          <t>15357</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15524</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9422</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27743</t>
+          <t>25967</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1948282</t>
+          <t>1948600</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1959906</t>
+          <t>1960056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1739068</t>
+          <t>1739814</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1750523</t>
+          <t>1751453</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3690806</t>
+          <t>3692582</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3708864</t>
+          <t>3709127</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15309</t>
+          <t>16456</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37224</t>
+          <t>37356</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13871</t>
+          <t>14512</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33071</t>
+          <t>34511</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33791</t>
+          <t>34412</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63083</t>
+          <t>63597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3382558</t>
+          <t>3382426</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3404473</t>
+          <t>3403326</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3517949</t>
+          <t>3516509</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3537149</t>
+          <t>3536508</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6907718</t>
+          <t>6907204</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6937010</t>
+          <t>6936389</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>11503</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14174</t>
+          <t>15399</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20621</t>
+          <t>20657</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>743150</t>
+          <t>742844</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>752536</t>
+          <t>752615</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>980486</t>
+          <t>979261</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>992639</t>
+          <t>992593</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1728386</t>
+          <t>1728350</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1743713</t>
+          <t>1743502</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22608</t>
+          <t>23881</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12563</t>
+          <t>12992</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11511</t>
+          <t>11544</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30247</t>
+          <t>30994</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2053777</t>
+          <t>2052504</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2069446</t>
+          <t>2069135</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1975737</t>
+          <t>1975308</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1986311</t>
+          <t>1986319</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4034438</t>
+          <t>4033691</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4053174</t>
+          <t>4053141</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15449</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>7232</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16758</t>
+          <t>17982</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531437</t>
+          <t>531911</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>544811</t>
+          <t>544959</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>542784</t>
+          <t>541908</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1079269</t>
+          <t>1078045</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1092396</t>
+          <t>1092325</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15427</t>
+          <t>15569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37608</t>
+          <t>37139</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23729</t>
+          <t>25176</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27019</t>
+          <t>28558</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53373</t>
+          <t>54667</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3340010</t>
+          <t>3340479</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3362191</t>
+          <t>3362049</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3508371</t>
+          <t>3506924</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3524409</t>
+          <t>3524745</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6856345</t>
+          <t>6855051</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6882699</t>
+          <t>6881160</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
